--- a/Design files/Right-Side/BOM/Client BOM-RIGHT-Bone_Conduction_Glasses.xlsx
+++ b/Design files/Right-Side/BOM/Client BOM-RIGHT-Bone_Conduction_Glasses.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="143">
   <si>
     <t>#</t>
   </si>
@@ -426,9 +426,6 @@
     <t>Battery</t>
   </si>
   <si>
-    <t>Transducer</t>
-  </si>
-  <si>
     <t>value</t>
   </si>
   <si>
@@ -442,6 +439,15 @@
   </si>
   <si>
     <t>Peripheral</t>
+  </si>
+  <si>
+    <t>3.7V Lithium Polymer Rechargeable Battery 501230 300mah</t>
+  </si>
+  <si>
+    <t>Bone Conduction Module Sensor Deafness Dumb Mini bone conduction horn speaker (GD02)</t>
+  </si>
+  <si>
+    <t>Transducer (GD02)</t>
   </si>
 </sst>
 </file>
@@ -666,9 +672,6 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -693,6 +696,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1007,10 +1013,10 @@
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="14"/>
-      <c r="L1" s="14"/>
+      <c r="I1" s="23"/>
+      <c r="J1" s="23"/>
+      <c r="K1" s="23"/>
+      <c r="L1" s="23"/>
     </row>
     <row r="2" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -1036,16 +1042,16 @@
         <v>102</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="J2" s="5" t="s">
         <v>132</v>
       </c>
       <c r="K2" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="L2" s="5" t="s">
         <v>137</v>
-      </c>
-      <c r="L2" s="5" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1064,7 +1070,7 @@
         <v>40</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G3" s="8" t="s">
         <v>65</v>
@@ -1115,7 +1121,7 @@
         <v>18</v>
       </c>
       <c r="K4" s="7">
-        <f t="shared" ref="K4:K26" si="1">J4*5</f>
+        <f t="shared" ref="K4:K28" si="1">J4*5</f>
         <v>90</v>
       </c>
       <c r="L4" s="9"/>
@@ -1388,7 +1394,7 @@
         <v>49</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G12" s="8" t="s">
         <v>89</v>
@@ -1409,40 +1415,40 @@
       <c r="L12" s="7"/>
     </row>
     <row r="13" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="19"/>
-      <c r="B13" s="20">
+      <c r="A13" s="18"/>
+      <c r="B13" s="19">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="C13" s="21" t="s">
+      <c r="C13" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="D13" s="15" t="s">
+      <c r="D13" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="E13" s="17" t="s">
+      <c r="E13" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="F13" s="15" t="s">
+      <c r="F13" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="G13" s="17" t="s">
+      <c r="G13" s="16" t="s">
         <v>90</v>
       </c>
-      <c r="H13" s="15" t="s">
+      <c r="H13" s="14" t="s">
         <v>106</v>
       </c>
-      <c r="I13" s="17" t="s">
+      <c r="I13" s="16" t="s">
         <v>122</v>
       </c>
-      <c r="J13" s="15">
+      <c r="J13" s="14">
         <v>1</v>
       </c>
-      <c r="K13" s="22">
+      <c r="K13" s="21">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L13" s="15"/>
+      <c r="L13" s="14"/>
     </row>
     <row r="14" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1"/>
@@ -1712,7 +1718,7 @@
         <v>58</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G21" s="8" t="s">
         <v>74</v>
@@ -1748,7 +1754,7 @@
         <v>59</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G22" s="8" t="s">
         <v>75</v>
@@ -1912,55 +1918,77 @@
       </c>
       <c r="L26" s="9"/>
     </row>
-    <row r="27" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="1"/>
       <c r="B27" s="11">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
       <c r="C27" s="13" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D27" s="9" t="s">
         <v>133</v>
       </c>
-      <c r="E27" s="10"/>
-      <c r="F27" s="9"/>
+      <c r="E27" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="F27" s="7" t="s">
+        <v>133</v>
+      </c>
       <c r="G27" s="10" t="s">
         <v>134</v>
       </c>
-      <c r="H27" s="9"/>
+      <c r="H27" s="7" t="s">
+        <v>133</v>
+      </c>
       <c r="I27" s="10" t="s">
         <v>133</v>
       </c>
-      <c r="J27" s="9"/>
-      <c r="K27" s="7"/>
+      <c r="J27" s="9">
+        <v>1</v>
+      </c>
+      <c r="K27" s="7">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
       <c r="L27" s="9"/>
     </row>
-    <row r="28" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:12" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="1"/>
       <c r="B28" s="11">
         <f>ROW(B28) - ROW($B$2)</f>
         <v>26</v>
       </c>
-      <c r="C28" s="23" t="s">
-        <v>140</v>
-      </c>
-      <c r="D28" s="16" t="s">
+      <c r="C28" s="22" t="s">
+        <v>139</v>
+      </c>
+      <c r="D28" s="15" t="s">
         <v>133</v>
       </c>
-      <c r="E28" s="18"/>
-      <c r="F28" s="16"/>
-      <c r="G28" s="18" t="s">
-        <v>135</v>
-      </c>
-      <c r="H28" s="16"/>
-      <c r="I28" s="18" t="s">
+      <c r="E28" s="15" t="s">
+        <v>141</v>
+      </c>
+      <c r="F28" s="15" t="s">
         <v>133</v>
       </c>
-      <c r="J28" s="16"/>
-      <c r="K28" s="16"/>
-      <c r="L28" s="16"/>
+      <c r="G28" s="15" t="s">
+        <v>142</v>
+      </c>
+      <c r="H28" s="15" t="s">
+        <v>133</v>
+      </c>
+      <c r="I28" s="17" t="s">
+        <v>133</v>
+      </c>
+      <c r="J28" s="15">
+        <v>1</v>
+      </c>
+      <c r="K28" s="15">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="L28" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/Design files/Right-Side/BOM/Client BOM-RIGHT-Bone_Conduction_Glasses.xlsx
+++ b/Design files/Right-Side/BOM/Client BOM-RIGHT-Bone_Conduction_Glasses.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="144">
   <si>
     <t>#</t>
   </si>
@@ -448,6 +448,9 @@
   </si>
   <si>
     <t>Transducer (GD02)</t>
+  </si>
+  <si>
+    <t>Touch Material</t>
   </si>
 </sst>
 </file>
@@ -987,7 +990,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:L28"/>
+  <dimension ref="A1:L29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3.140625" style="4" customWidth="1"/>
@@ -1093,7 +1096,7 @@
     <row r="4" spans="1:12" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1"/>
       <c r="B4" s="11">
-        <f t="shared" ref="B4:B27" si="0">ROW(B4) - ROW($B$2)</f>
+        <f t="shared" ref="B4:B28" si="0">ROW(B4) - ROW($B$2)</f>
         <v>2</v>
       </c>
       <c r="C4" s="13" t="s">
@@ -1121,7 +1124,7 @@
         <v>18</v>
       </c>
       <c r="K4" s="7">
-        <f t="shared" ref="K4:K28" si="1">J4*5</f>
+        <f t="shared" ref="K4:K29" si="1">J4*5</f>
         <v>90</v>
       </c>
       <c r="L4" s="9"/>
@@ -1954,41 +1957,74 @@
       </c>
       <c r="L27" s="9"/>
     </row>
-    <row r="28" spans="1:12" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="1"/>
       <c r="B28" s="11">
-        <f>ROW(B28) - ROW($B$2)</f>
+        <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="C28" s="22" t="s">
+      <c r="C28" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="D28" s="15" t="s">
+      <c r="D28" s="9" t="s">
         <v>133</v>
       </c>
-      <c r="E28" s="15" t="s">
+      <c r="E28" s="7"/>
+      <c r="F28" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="G28" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="H28" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="I28" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="J28" s="9">
+        <v>1</v>
+      </c>
+      <c r="K28" s="7">
+        <v>5</v>
+      </c>
+      <c r="L28" s="9"/>
+    </row>
+    <row r="29" spans="1:12" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="1"/>
+      <c r="B29" s="11">
+        <f>ROW(B29) - ROW($B$2)</f>
+        <v>27</v>
+      </c>
+      <c r="C29" s="22" t="s">
+        <v>139</v>
+      </c>
+      <c r="D29" s="15" t="s">
+        <v>133</v>
+      </c>
+      <c r="E29" s="15" t="s">
         <v>141</v>
       </c>
-      <c r="F28" s="15" t="s">
+      <c r="F29" s="15" t="s">
         <v>133</v>
       </c>
-      <c r="G28" s="15" t="s">
+      <c r="G29" s="15" t="s">
         <v>142</v>
       </c>
-      <c r="H28" s="15" t="s">
+      <c r="H29" s="15" t="s">
         <v>133</v>
       </c>
-      <c r="I28" s="17" t="s">
+      <c r="I29" s="17" t="s">
         <v>133</v>
       </c>
-      <c r="J28" s="15">
+      <c r="J29" s="15">
         <v>1</v>
       </c>
-      <c r="K28" s="15">
+      <c r="K29" s="15">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="L28" s="15"/>
+      <c r="L29" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="1">
